--- a/artifacts/import-templates/catalog-import-sample-workbook.xlsx
+++ b/artifacts/import-templates/catalog-import-sample-workbook.xlsx
@@ -55,7 +55,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -128,7 +128,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>{"variant":"dark-immersive","title":"Men's Atelier","imageUrl":"https://example.com/editorial/shop-men-hero.jpg"}</t>
+          <t>{"variant":"dark-immersive","title":"Men's Atelier","imageUrl":"https://lh3.googleusercontent.com/aida-public/AB6AXuACWMir-mH0L8UXbUXQWypp-pFR6ldBwMeB_P57xJ4h6lF91JgCYYyEJ27pPIbRuST3wzOd8tibscQ-NbIurAXAyGOUWfZstI5mdT9d5_jh6VLXet-x-y-OPWmMV69qNvZALg2WhY1PVY_SFZnR1pxtNpFxR9lsyyLR7XmqRbJ_dhy0WQE2rK_YiUzI2TXstgAkQ537sWLyCCgyHe5Z2QW16TODc2jAY392leqTD0jFdmPyw689W_PhHTFoOURRakfD2ODeVuxVtb-u"}</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -138,17 +138,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>{"title":"Men's Collection","description":"Shop the latest men's apparel"}</t>
+          <t>{"title":"Men's Atelier","description":"Structured menswear, tactile layering, and atelier outerwear seeded for local demos."}</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-09-26 10:00:00</t>
+          <t>2026-04-08 02:00:00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2025-09-26 10:00:00</t>
+          <t>2026-04-08 02:00:00</t>
         </is>
       </c>
     </row>
@@ -175,27 +175,121 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>{"variant":"light-editorial","title":"Women's Atelier","imageUrl":"https://example.com/editorial/atelier-women-hero.jpg"}</t>
+          <t>{"variant":"light-editorial","title":"Women's Atelier","imageUrl":"https://lh3.googleusercontent.com/aida-public/AB6AXuCCHjHHNBD0bZoSfUrXMIUsusvSJpfmxcJRzVyGEWriuKDCynB8NOcLil0MHJfUCfgjmGv_IMPAfbmEm73hz3s6Y6ycMQrKq1qnMzNHz4QbDczvsSfdf8SaL9vw3qoSEt36Xm52OFG4ej1BLs2XxqsJW_tPT1C2xruIyndF6i4KCKATXFKExblf5UqEURDlAYRnWNDYbLXe8GGoCndX4q2IeRKAuk6Etam3vFkW85HI4vZvrHKCLYN63hA-DGdTKTpY9k-VBO3aY4le"}</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[{"key":"size","kind":"sizes"},{"key":"color","kind":"palette"}]</t>
+          <t>[{"key":"size","kind":"sizes"},{"key":"color","kind":"palette"},{"key":"material","kind":"list"}]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>{"title":"Women's Atelier","description":"Discover refined silhouettes and seasonal edits"}</t>
+          <t>{"title":"Women's Atelier","description":"Quiet luxury silhouettes, soft structure, and tactile layers seeded for local demos."}</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2025-09-26 10:05:00</t>
+          <t>2026-04-08 02:05:00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2025-09-26 10:05:00</t>
+          <t>2026-04-08 02:05:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>{"variant":"workshop-editorial","title":"Footwear Atelier","imageUrl":"https://lh3.googleusercontent.com/aida-public/AB6AXuAFXvDME4hl86EBAExrs0TPuPyrDnhtwEb8MCDCvjzu2OS-kjWnUF7XkqwYs0MGf5WGZS6B5xPKLv0OXCG5ZrDjkm-McNkALLC0DCYp5LC9beGhY0SnzFUMFF998AElRWMoxze_NVDcZ1jJ4qerfPiE1xI5Xjc0Euy-lzfbdQzjbDW9gtsemGrCxPBq4MDAxVn_PdqcdHWaZ05cl7EMLinkvr6U9D8RGxe-UFtVaee5Q6n-Ohev-vr9h8DwExyawlWEZa9kUKDqsxlQ"}</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>[{"key":"size","kind":"sizes"},{"key":"material","kind":"list"},{"key":"type","kind":"list"}]</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>{"title":"Footwear Atelier","description":"Boots, loafers, sneakers, and handcrafted footwear seeded for local demos."}</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:10:00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:10:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>{"variant":"warm-object-study","title":"Accessories Atelier","imageUrl":"https://lh3.googleusercontent.com/aida-public/AB6AXuBlb713Ad1ZqSwci4xtZudIi3pLSP2LntjrYOZbjlMC3NLKbFllzQBjpelA2EcNqh24qXtAEpJDAyVB3yIDQIFXvkmKD86_5kVoAVPrMjID1bCAWG7fccKmwcS9kJ41ohvAPtYZJCMl2fOWYpy8JLZLlE7ksjMmFK7UnFdxUeGvbhsRltWVAsAFxPv7hkz1uizaDdvr0s5HWGulhxwsX6bDRakqRxoA2bYrvMeQA0Nta95LkdO9PMTmAYDvvqhCUeQTFYjDd4sXr9q0"}</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>[{"key":"category","kind":"list"},{"key":"material","kind":"list"}]</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>{"title":"Accessories Atelier","description":"Bags, jewelry, scarves, and finishing pieces seeded for local storefront demos."}</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:15:00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:15:00</t>
         </is>
       </c>
     </row>
@@ -205,7 +299,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -240,7 +334,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>men</t>
+          <t>shop-men</t>
         </is>
       </c>
     </row>
@@ -252,31 +346,235 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mens</t>
+          <t>Men</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>atelier-women</t>
+          <t>shop-men</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Atelier Women</t>
+          <t>men</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>shop-men</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mens</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>shop-men</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>nam</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>atelier-women</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>women-atelier</t>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Shop Women</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>atelier-women</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>shop-women</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>atelier-women</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>atelier-women</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>atelier-women</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>nu</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>atelier-women</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>atelier-women</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>shoes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>giay</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>footwear-atelier</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>accessory</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>phu kien</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>accessories-atelier</t>
         </is>
       </c>
     </row>
@@ -286,7 +584,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -344,7 +642,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>550e8400-e29b-41d4-a716-446655440000</t>
+          <t>10000000-0000-4000-8000-000000000001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -354,7 +652,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Linen Shirt</t>
+          <t>Sculpted Linen Shirt</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -364,18 +662,18 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>shop-men</t>
+          <t>Shop Men</t>
         </is>
       </c>
       <c r="F2">
-        <v>129.99</v>
+        <v>420</v>
       </c>
       <c r="G2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Italian Linen</t>
+          <t>Italian Linen Blend</t>
         </is>
       </c>
       <c r="I2">
@@ -383,14 +681,14 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2025-09-26 10:00:00</t>
+          <t>2026-04-08 02:01:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>550e8400-e29b-41d4-a716-446655440001</t>
+          <t>10000000-0000-4000-8000-000000000002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -400,7 +698,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cotton Tee</t>
+          <t>Structured Atelier Jacket</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -410,18 +708,18 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>shop-men</t>
+          <t>Shop Men</t>
         </is>
       </c>
       <c r="F3">
-        <v>49.99</v>
+        <v>1250</v>
       </c>
       <c r="G3">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Organic Cotton</t>
+          <t>100% Merino Wool</t>
         </is>
       </c>
       <c r="I3">
@@ -429,53 +727,2123 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2025-09-26 10:00:00</t>
+          <t>2026-04-08 02:02:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>550e8400-e29b-41d4-a716-446655440002</t>
+          <t>10000000-0000-4000-8000-000000000003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>SM-003</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Modern Drape Trousers</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>shop-men</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Shop Men</t>
+        </is>
+      </c>
+      <c r="F4">
+        <v>380</v>
+      </c>
+      <c r="G4">
+        <v>16</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fine Serge Cotton</t>
+        </is>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SM-004</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Atelier Knit Polo</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>shop-men</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Shop Men</t>
+        </is>
+      </c>
+      <c r="F5">
+        <v>290</v>
+      </c>
+      <c r="G5">
+        <v>18</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sea Island Cotton</t>
+        </is>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SM-005</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>The Obsidian Overcoat</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>shop-men</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Shop Men</t>
+        </is>
+      </c>
+      <c r="F6">
+        <v>1890</v>
+      </c>
+      <c r="G6">
+        <v>6</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Cashmere Blend</t>
+        </is>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:05:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SM-006</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Relaxed Cargo Trouser</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>shop-men</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Shop Men</t>
+        </is>
+      </c>
+      <c r="F7">
+        <v>340</v>
+      </c>
+      <c r="G7">
+        <v>14</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Brushed Twill</t>
+        </is>
+      </c>
+      <c r="I7">
+        <v>6</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:06:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SM-007</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Stonewashed Utility Overshirt</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>shop-men</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Shop Men</t>
+        </is>
+      </c>
+      <c r="F8">
+        <v>360</v>
+      </c>
+      <c r="G8">
+        <v>12</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Washed Cotton Drill</t>
+        </is>
+      </c>
+      <c r="I8">
+        <v>7</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SM-008</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Meridian Wool Cardigan</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>shop-men</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Shop Men</t>
+        </is>
+      </c>
+      <c r="F9">
+        <v>410</v>
+      </c>
+      <c r="G9">
+        <v>11</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Merino Wool</t>
+        </is>
+      </c>
+      <c r="I9">
+        <v>8</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SM-009</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Foundry Pleat Short</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>shop-men</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Shop Men</t>
+        </is>
+      </c>
+      <c r="F10">
+        <v>250</v>
+      </c>
+      <c r="G10">
+        <v>17</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Tumbled Cotton Poplin</t>
+        </is>
+      </c>
+      <c r="I10">
+        <v>9</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SM-010</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Tailored Poplin Bandshirt</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>shop-men</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Shop Men</t>
+        </is>
+      </c>
+      <c r="F11">
+        <v>280</v>
+      </c>
+      <c r="G11">
+        <v>20</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Compact Cotton Poplin</t>
+        </is>
+      </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:10:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SM-011</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Alpine Field Parka</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>shop-men</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Shop Men</t>
+        </is>
+      </c>
+      <c r="F12">
+        <v>980</v>
+      </c>
+      <c r="G12">
+        <v>8</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Technical Cotton Shell</t>
+        </is>
+      </c>
+      <c r="I12">
+        <v>11</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SM-012</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Slate Double Pleat Trouser</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>shop-men</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Shop Men</t>
+        </is>
+      </c>
+      <c r="F13">
+        <v>390</v>
+      </c>
+      <c r="G13">
+        <v>13</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Worsted Wool Blend</t>
+        </is>
+      </c>
+      <c r="I13">
+        <v>12</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>AW-001</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Silk Dress</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ethereal Silk Slip</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>atelier-women</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Atelier Women</t>
+        </is>
+      </c>
+      <c r="F14">
+        <v>340</v>
+      </c>
+      <c r="G14">
+        <v>10</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Mulberry Silk</t>
+        </is>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AW-002</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Architectural Overcoat</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>atelier-women</t>
         </is>
       </c>
-      <c r="F4">
-        <v>229.0</v>
-      </c>
-      <c r="G4">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Atelier Women</t>
+        </is>
+      </c>
+      <c r="F15">
+        <v>1250</v>
+      </c>
+      <c r="G15">
         <v>7</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Mulberry Silk</t>
-        </is>
-      </c>
-      <c r="I4">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Structured Wool Twill</t>
+        </is>
+      </c>
+      <c r="I15">
+        <v>2</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>AW-003</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Cloud Cashmere Crew</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>atelier-women</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Atelier Women</t>
+        </is>
+      </c>
+      <c r="F16">
+        <v>280</v>
+      </c>
+      <c r="G16">
+        <v>14</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Pure Cashmere</t>
+        </is>
+      </c>
+      <c r="I16">
+        <v>3</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:13:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>AW-004</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Sculptural Pleated Skirt</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>atelier-women</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Atelier Women</t>
+        </is>
+      </c>
+      <c r="F17">
+        <v>490</v>
+      </c>
+      <c r="G17">
+        <v>12</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Pleated Wool Crepe</t>
+        </is>
+      </c>
+      <c r="I17">
+        <v>4</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>AW-005</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Hearth Tapered Pant</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>atelier-women</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Atelier Women</t>
+        </is>
+      </c>
+      <c r="F18">
+        <v>320</v>
+      </c>
+      <c r="G18">
+        <v>16</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Brushed Wool Blend</t>
+        </is>
+      </c>
+      <c r="I18">
+        <v>5</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:15:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>AW-006</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Atelier Formal Blazer</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>atelier-women</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Atelier Women</t>
+        </is>
+      </c>
+      <c r="F19">
+        <v>850</v>
+      </c>
+      <c r="G19">
+        <v>9</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Tailored Wool Blend</t>
+        </is>
+      </c>
+      <c r="I19">
+        <v>6</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:16:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>AW-007</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Botanical Wrap Dress</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>atelier-women</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Atelier Women</t>
+        </is>
+      </c>
+      <c r="F20">
+        <v>410</v>
+      </c>
+      <c r="G20">
+        <v>11</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Washed Silk Blend</t>
+        </is>
+      </c>
+      <c r="I20">
+        <v>7</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:17:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>AW-008</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Gallery Satin Blouse</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>atelier-women</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Atelier Women</t>
+        </is>
+      </c>
+      <c r="F21">
+        <v>295</v>
+      </c>
+      <c r="G21">
+        <v>15</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Liquid Satin</t>
+        </is>
+      </c>
+      <c r="I21">
+        <v>8</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:18:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>AW-009</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Quiet Wool Column Coat</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>atelier-women</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Atelier Women</t>
+        </is>
+      </c>
+      <c r="F22">
+        <v>1180</v>
+      </c>
+      <c r="G22">
+        <v>6</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Double-Faced Wool</t>
+        </is>
+      </c>
+      <c r="I22">
+        <v>9</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:19:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>AW-010</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Soft Structure Trouser</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>atelier-women</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Atelier Women</t>
+        </is>
+      </c>
+      <c r="F23">
+        <v>365</v>
+      </c>
+      <c r="G23">
+        <v>13</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Compact Viscose Twill</t>
+        </is>
+      </c>
+      <c r="I23">
+        <v>10</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:20:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>AW-011</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Moonstone Rib Tank</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>atelier-women</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Atelier Women</t>
+        </is>
+      </c>
+      <c r="F24">
+        <v>180</v>
+      </c>
+      <c r="G24">
+        <v>18</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Fine Rib Cotton</t>
+        </is>
+      </c>
+      <c r="I24">
+        <v>11</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:21:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>AW-012</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Atelier Bias Midi Skirt</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>atelier-women</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Atelier Women</t>
+        </is>
+      </c>
+      <c r="F25">
+        <v>430</v>
+      </c>
+      <c r="G25">
+        <v>10</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Washed Satin</t>
+        </is>
+      </c>
+      <c r="I25">
+        <v>12</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:22:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FW-001</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Atelier Low Sneaker</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="F26">
+        <v>340</v>
+      </c>
+      <c r="G26">
+        <v>18</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Smooth Italian Calfskin</t>
+        </is>
+      </c>
+      <c r="I26">
         <v>1</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2025-09-26 10:05:00</t>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:21:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FW-002</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Chelsea Field Boot</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="F27">
+        <v>495</v>
+      </c>
+      <c r="G27">
+        <v>11</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Waxed Roughout Leather</t>
+        </is>
+      </c>
+      <c r="I27">
+        <v>2</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:22:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FW-003</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Classic Penny Loafer</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="F28">
+        <v>420</v>
+      </c>
+      <c r="G28">
+        <v>12</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Pebbled Grain Leather</t>
+        </is>
+      </c>
+      <c r="I28">
+        <v>3</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:23:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FW-004</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Moc Toe Service Boot</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="F29">
+        <v>560</v>
+      </c>
+      <c r="G29">
+        <v>9</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>English Bridle Leather</t>
+        </is>
+      </c>
+      <c r="I29">
+        <v>4</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:24:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FW-005</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ridge Runner Hiker</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="F30">
+        <v>610</v>
+      </c>
+      <c r="G30">
+        <v>8</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Stormwelt Bridle Leather</t>
+        </is>
+      </c>
+      <c r="I30">
+        <v>5</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:25:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>FW-006</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Polished Derby Loafer</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="F31">
+        <v>450</v>
+      </c>
+      <c r="G31">
+        <v>10</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Polished Grain Leather</t>
+        </is>
+      </c>
+      <c r="I31">
+        <v>6</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:26:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>FW-007</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Slate Suede Desert Boot</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="F32">
+        <v>470</v>
+      </c>
+      <c r="G32">
+        <v>10</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Premium Suede</t>
+        </is>
+      </c>
+      <c r="I32">
+        <v>7</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:27:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>FW-008</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Court Leather Trainer</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="F33">
+        <v>360</v>
+      </c>
+      <c r="G33">
+        <v>16</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Full-Grain Calfskin</t>
+        </is>
+      </c>
+      <c r="I33">
+        <v>8</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:28:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>FW-009</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Artisan Monk Strap</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="F34">
+        <v>530</v>
+      </c>
+      <c r="G34">
+        <v>7</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Hand-Burnished Grain Leather</t>
+        </is>
+      </c>
+      <c r="I34">
+        <v>9</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:29:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>FW-010</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Pebble Driving Loafer</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="F35">
+        <v>390</v>
+      </c>
+      <c r="G35">
+        <v>12</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Pebbled Grain Leather</t>
+        </is>
+      </c>
+      <c r="I35">
+        <v>10</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>FW-011</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Harbor Fisher Sandal</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="F36">
+        <v>310</v>
+      </c>
+      <c r="G36">
+        <v>14</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Matte Calfskin</t>
+        </is>
+      </c>
+      <c r="I36">
+        <v>11</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:31:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>FW-012</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Iron Commute Boot</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Footwear</t>
+        </is>
+      </c>
+      <c r="F37">
+        <v>580</v>
+      </c>
+      <c r="G37">
+        <v>8</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Weatherproof Bridle Leather</t>
+        </is>
+      </c>
+      <c r="I37">
+        <v>12</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:32:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>AC-001</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Atelier Tote</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F38">
+        <v>840</v>
+      </c>
+      <c r="G38">
+        <v>9</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Vegetable Tanned Leather</t>
+        </is>
+      </c>
+      <c r="I38">
+        <v>1</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:31:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>AC-002</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Aurora Wrap</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F39">
+        <v>215</v>
+      </c>
+      <c r="G39">
+        <v>18</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Organic Raw Silk</t>
+        </is>
+      </c>
+      <c r="I39">
+        <v>2</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:32:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>AC-003</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Cintura Belt</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F40">
+        <v>165</v>
+      </c>
+      <c r="G40">
+        <v>20</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Full Grain Saddle Leather</t>
+        </is>
+      </c>
+      <c r="I40">
+        <v>3</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:33:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>AC-004</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Vault Clutch</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F41">
+        <v>420</v>
+      </c>
+      <c r="G41">
+        <v>10</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Nappa Leather</t>
+        </is>
+      </c>
+      <c r="I41">
+        <v>4</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:34:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>AC-005</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Obsidian Band</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F42">
+        <v>310</v>
+      </c>
+      <c r="G42">
+        <v>12</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>925 Sterling Silver</t>
+        </is>
+      </c>
+      <c r="I42">
+        <v>5</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:35:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>AC-006</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Mist Scarf</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F43">
+        <v>190</v>
+      </c>
+      <c r="G43">
+        <v>16</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Cashmere Blend</t>
+        </is>
+      </c>
+      <c r="I43">
+        <v>6</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:36:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>AC-007</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Meridian Weekender</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F44">
+        <v>980</v>
+      </c>
+      <c r="G44">
+        <v>7</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Vachetta Leather</t>
+        </is>
+      </c>
+      <c r="I44">
+        <v>7</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:37:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>AC-008</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Sculptor Card Holder</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F45">
+        <v>145</v>
+      </c>
+      <c r="G45">
+        <v>15</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Vachetta Leather</t>
+        </is>
+      </c>
+      <c r="I45">
+        <v>8</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:38:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>AC-009</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Studio Key Lanyard</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F46">
+        <v>110</v>
+      </c>
+      <c r="G46">
+        <v>14</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Bridle Leather</t>
+        </is>
+      </c>
+      <c r="I46">
+        <v>9</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:39:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>AC-010</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Veil Silk Neckerchief</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F47">
+        <v>175</v>
+      </c>
+      <c r="G47">
+        <v>17</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Printed Raw Silk</t>
+        </is>
+      </c>
+      <c r="I47">
+        <v>10</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:40:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>AC-011</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Hinge Cuff</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F48">
+        <v>265</v>
+      </c>
+      <c r="G48">
+        <v>11</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sterling Silver</t>
+        </is>
+      </c>
+      <c r="I48">
+        <v>11</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:41:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>10000000-0000-4000-8000-000000000048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>AC-012</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Atelier Bucket Pouch</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="F49">
+        <v>390</v>
+      </c>
+      <c r="G49">
+        <v>9</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Nappa Leather</t>
+        </is>
+      </c>
+      <c r="I49">
+        <v>12</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-04-08 02:42:00</t>
         </is>
       </c>
     </row>
@@ -485,7 +2853,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,7 +2901,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>660e8400-e29b-41d4-a716-446655440000</t>
+          <t>20000000-0000-4000-8000-000000000001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -553,25 +2921,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Oat</t>
         </is>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G2">
-        <v>129.99</v>
+        <v>420</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://example.com/images/sm001-m.jpg</t>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuBRTlahnsv0f7ya3xU5YTERBeygNv3B_6MEExHsUzTI3uGv3gn9RVVaVkXFHJAQIYeO-NnQ-n51wqkjA-oml_uoLI96mxp1piJxtPHA5ofpE_9tSdHTMa8lNfjCgdbUOSRi__Y4J8VFSz5HhI5ZB9C5Vl5zl-6FxNxhAYwEDNV_XOP2dGsj5rTUtGDd1a59qGSue1hdS28wAOq4_SpG152HGpLir9kJsPtGA9trmPt5raubxkNMY1AI1cI7Qs5-pnKuSFT_JrLZrEaz</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>660e8400-e29b-41d4-a716-446655440001</t>
+          <t>20000000-0000-4000-8000-000000000002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -591,25 +2959,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Oat</t>
         </is>
       </c>
       <c r="F3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G3">
-        <v>129.99</v>
+        <v>420</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://example.com/images/sm001-l.jpg</t>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuBRTlahnsv0f7ya3xU5YTERBeygNv3B_6MEExHsUzTI3uGv3gn9RVVaVkXFHJAQIYeO-NnQ-n51wqkjA-oml_uoLI96mxp1piJxtPHA5ofpE_9tSdHTMa8lNfjCgdbUOSRi__Y4J8VFSz5HhI5ZB9C5Vl5zl-6FxNxhAYwEDNV_XOP2dGsj5rTUtGDd1a59qGSue1hdS28wAOq4_SpG152HGpLir9kJsPtGA9trmPt5raubxkNMY1AI1cI7Qs5-pnKuSFT_JrLZrEaz</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>660e8400-e29b-41d4-a716-446655440002</t>
+          <t>20000000-0000-4000-8000-000000000003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -619,28 +2987,3172 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SM-002-S</t>
+          <t>SM-002-M</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Charcoal</t>
+        </is>
+      </c>
+      <c r="F4">
+        <v>5</v>
+      </c>
+      <c r="G4">
+        <v>1250</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuA004mNLReNQb9OI2U6JwpX4idr5HiAL2OAqj-X2r60qRDaMIYLE7YAWWdvJ6_uvkh1jgDweWN2QRC0Z6CnAXNS54x6M_Qkf8uPtTr4G6Cl5-Y5z8iuGvbIv1u_DCawCRbkf01JSFMi_iZ2APFb_m56yIPq8-_Ap7HY-QbhgAL2tc-tsE4VsnyibszwQjgYBz28AGgGUIIQ7EDmY1bXGdkXyNQI991VG2ouIlVK-wOCqK_Lq8GNj4h27eldl1LjnR6Wt903BlKnHCVn</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SM-002</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SM-002-L</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Charcoal</t>
+        </is>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>1250</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuA004mNLReNQb9OI2U6JwpX4idr5HiAL2OAqj-X2r60qRDaMIYLE7YAWWdvJ6_uvkh1jgDweWN2QRC0Z6CnAXNS54x6M_Qkf8uPtTr4G6Cl5-Y5z8iuGvbIv1u_DCawCRbkf01JSFMi_iZ2APFb_m56yIPq8-_Ap7HY-QbhgAL2tc-tsE4VsnyibszwQjgYBz28AGgGUIIQ7EDmY1bXGdkXyNQI991VG2ouIlVK-wOCqK_Lq8GNj4h27eldl1LjnR6Wt903BlKnHCVn</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SM-003</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SM-003-M</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Olive</t>
+        </is>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>380</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuBXRSWOWcHtCNyaMDYLCJzvRD_aYObkVBkIHPoz_HZOOuihWxPKo82MAX7anUmfBqHwOgx_6YthGokOn-aqEtAkMya3di9RNTlqqA2-zqT6x85Yh0CGWy5_gOTjOOMYxnRJ7B8A9ihZaMR-PzIAILb7T5rSMUCiZ-3CZRTX_u3XxJpOlXlYjWEZj4aFLaV_mamuWkKjkhTxSRpw7LyICx9lPITcKUuGOxJ0NkpKweDI4rMjqFkSSGZJssErigmmpbKq5Z6kLPVUehXg</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SM-003</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SM-003-L</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Olive</t>
+        </is>
+      </c>
+      <c r="F7">
+        <v>8</v>
+      </c>
+      <c r="G7">
+        <v>380</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuBXRSWOWcHtCNyaMDYLCJzvRD_aYObkVBkIHPoz_HZOOuihWxPKo82MAX7anUmfBqHwOgx_6YthGokOn-aqEtAkMya3di9RNTlqqA2-zqT6x85Yh0CGWy5_gOTjOOMYxnRJ7B8A9ihZaMR-PzIAILb7T5rSMUCiZ-3CZRTX_u3XxJpOlXlYjWEZj4aFLaV_mamuWkKjkhTxSRpw7LyICx9lPITcKUuGOxJ0NkpKweDI4rMjqFkSSGZJssErigmmpbKq5Z6kLPVUehXg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SM-004</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SM-004-M</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Forest</t>
+        </is>
+      </c>
+      <c r="F8">
+        <v>9</v>
+      </c>
+      <c r="G8">
+        <v>290</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuDBowt2AR0QGkZ_teHLK0qG2iUl8fGSUuNTrZHreU_s95xtmrbnCTB8LYOShnHaraaNDqoUnziBnVe2Rh6OAlJpU9ZSpF84L0-k23aokXc6aJdWswRdyGowycFswnENPgO9tfnUyUaMa2VjW8lGJYkmhPbnJhSE0zC0BdoSTdae8pmGnQwaAXzVlJJRhWYysiO1yf2n_lREj8nVxarkGub1OLnfLI4QrhAiAGV-AZTWnZg1MCqdpNi1pBSjb6RIPFAzXw0h_iTQCqrp</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SM-004</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SM-004-L</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Forest</t>
+        </is>
+      </c>
+      <c r="F9">
+        <v>9</v>
+      </c>
+      <c r="G9">
+        <v>290</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuDBowt2AR0QGkZ_teHLK0qG2iUl8fGSUuNTrZHreU_s95xtmrbnCTB8LYOShnHaraaNDqoUnziBnVe2Rh6OAlJpU9ZSpF84L0-k23aokXc6aJdWswRdyGowycFswnENPgO9tfnUyUaMa2VjW8lGJYkmhPbnJhSE0zC0BdoSTdae8pmGnQwaAXzVlJJRhWYysiO1yf2n_lREj8nVxarkGub1OLnfLI4QrhAiAGV-AZTWnZg1MCqdpNi1pBSjb6RIPFAzXw0h_iTQCqrp</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SM-005</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SM-005-L</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="F10">
+        <v>3</v>
+      </c>
+      <c r="G10">
+        <v>1890</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuDb4HgZThk-i_juM7LnHT28IvYp6L3O-BYlcwDKgfj8NoIfTFFhOF2Ole0eBVsqpYg3jj_0TeLOFVAlmWeCOqcLhMrp0WOXtTgYUke-t7sj7lC-e4jEl3lE8aZs01lCVJenptBJf3Fh0f1sdTVQ9W0cWZD8hEtVjX-LK-Bsqoc2UzdzkTUWeVjp7hrhjMGZhuTtvQ56nTXVelw9_F3p1d8ryVxqAzayeUimjbfSI8FHukDr7r45A4VjAJ3lpymfXulGrEM83TxdK6Sj</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SM-005</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SM-005-XL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="F11">
+        <v>3</v>
+      </c>
+      <c r="G11">
+        <v>1890</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuDb4HgZThk-i_juM7LnHT28IvYp6L3O-BYlcwDKgfj8NoIfTFFhOF2Ole0eBVsqpYg3jj_0TeLOFVAlmWeCOqcLhMrp0WOXtTgYUke-t7sj7lC-e4jEl3lE8aZs01lCVJenptBJf3Fh0f1sdTVQ9W0cWZD8hEtVjX-LK-Bsqoc2UzdzkTUWeVjp7hrhjMGZhuTtvQ56nTXVelw9_F3p1d8ryVxqAzayeUimjbfSI8FHukDr7r45A4VjAJ3lpymfXulGrEM83TxdK6Sj</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SM-006</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SM-006-S</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Navy</t>
-        </is>
-      </c>
-      <c r="F4">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Khaki</t>
+        </is>
+      </c>
+      <c r="F12">
+        <v>7</v>
+      </c>
+      <c r="G12">
+        <v>340</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuBRTlahnsv0f7ya3xU5YTERBeygNv3B_6MEExHsUzTI3uGv3gn9RVVaVkXFHJAQIYeO-NnQ-n51wqkjA-oml_uoLI96mxp1piJxtPHA5ofpE_9tSdHTMa8lNfjCgdbUOSRi__Y4J8VFSz5HhI5ZB9C5Vl5zl-6FxNxhAYwEDNV_XOP2dGsj5rTUtGDd1a59qGSue1hdS28wAOq4_SpG152HGpLir9kJsPtGA9trmPt5raubxkNMY1AI1cI7Qs5-pnKuSFT_JrLZrEaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SM-006</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SM-006-M</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Khaki</t>
+        </is>
+      </c>
+      <c r="F13">
+        <v>7</v>
+      </c>
+      <c r="G13">
+        <v>340</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuBRTlahnsv0f7ya3xU5YTERBeygNv3B_6MEExHsUzTI3uGv3gn9RVVaVkXFHJAQIYeO-NnQ-n51wqkjA-oml_uoLI96mxp1piJxtPHA5ofpE_9tSdHTMa8lNfjCgdbUOSRi__Y4J8VFSz5HhI5ZB9C5Vl5zl-6FxNxhAYwEDNV_XOP2dGsj5rTUtGDd1a59qGSue1hdS28wAOq4_SpG152HGpLir9kJsPtGA9trmPt5raubxkNMY1AI1cI7Qs5-pnKuSFT_JrLZrEaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SM-007</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SM-007-M</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Stone</t>
+        </is>
+      </c>
+      <c r="F14">
+        <v>6</v>
+      </c>
+      <c r="G14">
+        <v>360</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuA004mNLReNQb9OI2U6JwpX4idr5HiAL2OAqj-X2r60qRDaMIYLE7YAWWdvJ6_uvkh1jgDweWN2QRC0Z6CnAXNS54x6M_Qkf8uPtTr4G6Cl5-Y5z8iuGvbIv1u_DCawCRbkf01JSFMi_iZ2APFb_m56yIPq8-_Ap7HY-QbhgAL2tc-tsE4VsnyibszwQjgYBz28AGgGUIIQ7EDmY1bXGdkXyNQI991VG2ouIlVK-wOCqK_Lq8GNj4h27eldl1LjnR6Wt903BlKnHCVn</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SM-007</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SM-007-L</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Stone</t>
+        </is>
+      </c>
+      <c r="F15">
+        <v>6</v>
+      </c>
+      <c r="G15">
+        <v>360</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuA004mNLReNQb9OI2U6JwpX4idr5HiAL2OAqj-X2r60qRDaMIYLE7YAWWdvJ6_uvkh1jgDweWN2QRC0Z6CnAXNS54x6M_Qkf8uPtTr4G6Cl5-Y5z8iuGvbIv1u_DCawCRbkf01JSFMi_iZ2APFb_m56yIPq8-_Ap7HY-QbhgAL2tc-tsE4VsnyibszwQjgYBz28AGgGUIIQ7EDmY1bXGdkXyNQI991VG2ouIlVK-wOCqK_Lq8GNj4h27eldl1LjnR6Wt903BlKnHCVn</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SM-008</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SM-008-M</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Graphite</t>
+        </is>
+      </c>
+      <c r="F16">
+        <v>6</v>
+      </c>
+      <c r="G16">
+        <v>410</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuBXRSWOWcHtCNyaMDYLCJzvRD_aYObkVBkIHPoz_HZOOuihWxPKo82MAX7anUmfBqHwOgx_6YthGokOn-aqEtAkMya3di9RNTlqqA2-zqT6x85Yh0CGWy5_gOTjOOMYxnRJ7B8A9ihZaMR-PzIAILb7T5rSMUCiZ-3CZRTX_u3XxJpOlXlYjWEZj4aFLaV_mamuWkKjkhTxSRpw7LyICx9lPITcKUuGOxJ0NkpKweDI4rMjqFkSSGZJssErigmmpbKq5Z6kLPVUehXg</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SM-008</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SM-008-L</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Graphite</t>
+        </is>
+      </c>
+      <c r="F17">
+        <v>5</v>
+      </c>
+      <c r="G17">
+        <v>410</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuBXRSWOWcHtCNyaMDYLCJzvRD_aYObkVBkIHPoz_HZOOuihWxPKo82MAX7anUmfBqHwOgx_6YthGokOn-aqEtAkMya3di9RNTlqqA2-zqT6x85Yh0CGWy5_gOTjOOMYxnRJ7B8A9ihZaMR-PzIAILb7T5rSMUCiZ-3CZRTX_u3XxJpOlXlYjWEZj4aFLaV_mamuWkKjkhTxSRpw7LyICx9lPITcKUuGOxJ0NkpKweDI4rMjqFkSSGZJssErigmmpbKq5Z6kLPVUehXg</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SM-009</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SM-009-S</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sand</t>
+        </is>
+      </c>
+      <c r="F18">
+        <v>9</v>
+      </c>
+      <c r="G18">
+        <v>250</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuDBowt2AR0QGkZ_teHLK0qG2iUl8fGSUuNTrZHreU_s95xtmrbnCTB8LYOShnHaraaNDqoUnziBnVe2Rh6OAlJpU9ZSpF84L0-k23aokXc6aJdWswRdyGowycFswnENPgO9tfnUyUaMa2VjW8lGJYkmhPbnJhSE0zC0BdoSTdae8pmGnQwaAXzVlJJRhWYysiO1yf2n_lREj8nVxarkGub1OLnfLI4QrhAiAGV-AZTWnZg1MCqdpNi1pBSjb6RIPFAzXw0h_iTQCqrp</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SM-009</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SM-009-M</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sand</t>
+        </is>
+      </c>
+      <c r="F19">
+        <v>8</v>
+      </c>
+      <c r="G19">
+        <v>250</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuDBowt2AR0QGkZ_teHLK0qG2iUl8fGSUuNTrZHreU_s95xtmrbnCTB8LYOShnHaraaNDqoUnziBnVe2Rh6OAlJpU9ZSpF84L0-k23aokXc6aJdWswRdyGowycFswnENPgO9tfnUyUaMa2VjW8lGJYkmhPbnJhSE0zC0BdoSTdae8pmGnQwaAXzVlJJRhWYysiO1yf2n_lREj8nVxarkGub1OLnfLI4QrhAiAGV-AZTWnZg1MCqdpNi1pBSjb6RIPFAzXw0h_iTQCqrp</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SM-010</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SM-010-M</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="F20">
+        <v>10</v>
+      </c>
+      <c r="G20">
+        <v>280</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuDb4HgZThk-i_juM7LnHT28IvYp6L3O-BYlcwDKgfj8NoIfTFFhOF2Ole0eBVsqpYg3jj_0TeLOFVAlmWeCOqcLhMrp0WOXtTgYUke-t7sj7lC-e4jEl3lE8aZs01lCVJenptBJf3Fh0f1sdTVQ9W0cWZD8hEtVjX-LK-Bsqoc2UzdzkTUWeVjp7hrhjMGZhuTtvQ56nTXVelw9_F3p1d8ryVxqAzayeUimjbfSI8FHukDr7r45A4VjAJ3lpymfXulGrEM83TxdK6Sj</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SM-010</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SM-010-L</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="F21">
+        <v>10</v>
+      </c>
+      <c r="G21">
+        <v>280</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuDb4HgZThk-i_juM7LnHT28IvYp6L3O-BYlcwDKgfj8NoIfTFFhOF2Ole0eBVsqpYg3jj_0TeLOFVAlmWeCOqcLhMrp0WOXtTgYUke-t7sj7lC-e4jEl3lE8aZs01lCVJenptBJf3Fh0f1sdTVQ9W0cWZD8hEtVjX-LK-Bsqoc2UzdzkTUWeVjp7hrhjMGZhuTtvQ56nTXVelw9_F3p1d8ryVxqAzayeUimjbfSI8FHukDr7r45A4VjAJ3lpymfXulGrEM83TxdK6Sj</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SM-011</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SM-011-L</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Moss</t>
+        </is>
+      </c>
+      <c r="F22">
+        <v>4</v>
+      </c>
+      <c r="G22">
+        <v>980</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuBRTlahnsv0f7ya3xU5YTERBeygNv3B_6MEExHsUzTI3uGv3gn9RVVaVkXFHJAQIYeO-NnQ-n51wqkjA-oml_uoLI96mxp1piJxtPHA5ofpE_9tSdHTMa8lNfjCgdbUOSRi__Y4J8VFSz5HhI5ZB9C5Vl5zl-6FxNxhAYwEDNV_XOP2dGsj5rTUtGDd1a59qGSue1hdS28wAOq4_SpG152HGpLir9kJsPtGA9trmPt5raubxkNMY1AI1cI7Qs5-pnKuSFT_JrLZrEaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SM-011</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SM-011-XL</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Moss</t>
+        </is>
+      </c>
+      <c r="F23">
+        <v>4</v>
+      </c>
+      <c r="G23">
+        <v>980</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuBRTlahnsv0f7ya3xU5YTERBeygNv3B_6MEExHsUzTI3uGv3gn9RVVaVkXFHJAQIYeO-NnQ-n51wqkjA-oml_uoLI96mxp1piJxtPHA5ofpE_9tSdHTMa8lNfjCgdbUOSRi__Y4J8VFSz5HhI5ZB9C5Vl5zl-6FxNxhAYwEDNV_XOP2dGsj5rTUtGDd1a59qGSue1hdS28wAOq4_SpG152HGpLir9kJsPtGA9trmPt5raubxkNMY1AI1cI7Qs5-pnKuSFT_JrLZrEaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SM-012</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SM-012-M</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Slate</t>
+        </is>
+      </c>
+      <c r="F24">
+        <v>7</v>
+      </c>
+      <c r="G24">
+        <v>390</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuA004mNLReNQb9OI2U6JwpX4idr5HiAL2OAqj-X2r60qRDaMIYLE7YAWWdvJ6_uvkh1jgDweWN2QRC0Z6CnAXNS54x6M_Qkf8uPtTr4G6Cl5-Y5z8iuGvbIv1u_DCawCRbkf01JSFMi_iZ2APFb_m56yIPq8-_Ap7HY-QbhgAL2tc-tsE4VsnyibszwQjgYBz28AGgGUIIQ7EDmY1bXGdkXyNQI991VG2ouIlVK-wOCqK_Lq8GNj4h27eldl1LjnR6Wt903BlKnHCVn</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SM-012</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SM-012-L</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Slate</t>
+        </is>
+      </c>
+      <c r="F25">
+        <v>6</v>
+      </c>
+      <c r="G25">
+        <v>390</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuA004mNLReNQb9OI2U6JwpX4idr5HiAL2OAqj-X2r60qRDaMIYLE7YAWWdvJ6_uvkh1jgDweWN2QRC0Z6CnAXNS54x6M_Qkf8uPtTr4G6Cl5-Y5z8iuGvbIv1u_DCawCRbkf01JSFMi_iZ2APFb_m56yIPq8-_Ap7HY-QbhgAL2tc-tsE4VsnyibszwQjgYBz28AGgGUIIQ7EDmY1bXGdkXyNQI991VG2ouIlVK-wOCqK_Lq8GNj4h27eldl1LjnR6Wt903BlKnHCVn</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>AW-001</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AW-001-S</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Cream</t>
+        </is>
+      </c>
+      <c r="F26">
+        <v>5</v>
+      </c>
+      <c r="G26">
+        <v>340</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuA2sL_3eVTxv8pTPhQFFFpSQH6Kaq9or00Ox__PprWsxnH4iFcdyvkF6yE_uLy_crNRWln5sUDsqQmSo-iayh_0MyCYYTR20XSGjWAB-uNe6duE69pSu714RVSt74tQMEIF3fuTduw02xllANi1JDAtn12UeUh9ljLf8hz3xi6jPfnSdYWCX7w9y3IwSDyovmYmtsxb0x9P-3bKU5qLNiMw7cc4_t2zNEpT8QLPRQLTFIXGR2WRSQbgpFitN5ZgjO-BIsY_4Wyg7jRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>AW-001</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AW-001-M</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Cream</t>
+        </is>
+      </c>
+      <c r="F27">
+        <v>5</v>
+      </c>
+      <c r="G27">
+        <v>340</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuA2sL_3eVTxv8pTPhQFFFpSQH6Kaq9or00Ox__PprWsxnH4iFcdyvkF6yE_uLy_crNRWln5sUDsqQmSo-iayh_0MyCYYTR20XSGjWAB-uNe6duE69pSu714RVSt74tQMEIF3fuTduw02xllANi1JDAtn12UeUh9ljLf8hz3xi6jPfnSdYWCX7w9y3IwSDyovmYmtsxb0x9P-3bKU5qLNiMw7cc4_t2zNEpT8QLPRQLTFIXGR2WRSQbgpFitN5ZgjO-BIsY_4Wyg7jRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>AW-002</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AW-002-M</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Forest</t>
+        </is>
+      </c>
+      <c r="F28">
+        <v>4</v>
+      </c>
+      <c r="G28">
+        <v>1250</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuBmKXEwtGPg000dRd0DYpkc78_z_0z7Q60H3fju2rnkDAllnKGSFzesSqKvn2OqncI_k-QRIvUyfVSm75I-UKw3DhxiM5eOINn4C-vJnvj2z8uKIL2AqGnXgvmqeYEEzJ5-il3zT3BTGt9iPabLxhcPbK9AwTzCM3Z9Fo3vrhfReTlHCTZ3EIgs7_JxhOFfmrNerCamtXr0QKPKlok1p5W71S8CFoXMlgrk9yrqe55hyi8oG24OwLIfOD6sAGZDuAtdrYmvQ0QD-hzg</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>AW-002</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AW-002-L</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Forest</t>
+        </is>
+      </c>
+      <c r="F29">
+        <v>3</v>
+      </c>
+      <c r="G29">
+        <v>1250</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuBmKXEwtGPg000dRd0DYpkc78_z_0z7Q60H3fju2rnkDAllnKGSFzesSqKvn2OqncI_k-QRIvUyfVSm75I-UKw3DhxiM5eOINn4C-vJnvj2z8uKIL2AqGnXgvmqeYEEzJ5-il3zT3BTGt9iPabLxhcPbK9AwTzCM3Z9Fo3vrhfReTlHCTZ3EIgs7_JxhOFfmrNerCamtXr0QKPKlok1p5W71S8CFoXMlgrk9yrqe55hyi8oG24OwLIfOD6sAGZDuAtdrYmvQ0QD-hzg</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>AW-003</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AW-003-M</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Stone</t>
+        </is>
+      </c>
+      <c r="F30">
+        <v>7</v>
+      </c>
+      <c r="G30">
+        <v>280</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuBEKFEZ7Xk7Fyqc9Uf8Rr7JfhPIghhY7j0HO6bqSglckdRAUU1XFK1Vy_uPXAbpLqczXmCH41FFfT4QIgBtt7oBHhaEojRqYoMhEeW0zN9yDlgFxnnAhZfa_FjmfnZNakXUp-HAT6D2gb_BUeHA5TXBmMVsObd_AHQfOwPuMZTKrAqSkXnJe60KUnlOWajJ6btQ5zyNadwls33tVZNcDlHyJ8_EUlUAhHRtQ90ZhEzMNN5Mzjf_Hr7Onn7MZF-hkz45XkPrdm6pngSw</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>AW-003</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AW-003-L</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Stone</t>
+        </is>
+      </c>
+      <c r="F31">
+        <v>7</v>
+      </c>
+      <c r="G31">
+        <v>280</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuBEKFEZ7Xk7Fyqc9Uf8Rr7JfhPIghhY7j0HO6bqSglckdRAUU1XFK1Vy_uPXAbpLqczXmCH41FFfT4QIgBtt7oBHhaEojRqYoMhEeW0zN9yDlgFxnnAhZfa_FjmfnZNakXUp-HAT6D2gb_BUeHA5TXBmMVsObd_AHQfOwPuMZTKrAqSkXnJe60KUnlOWajJ6btQ5zyNadwls33tVZNcDlHyJ8_EUlUAhHRtQ90ZhEzMNN5Mzjf_Hr7Onn7MZF-hkz45XkPrdm6pngSw</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>AW-004</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AW-004-S</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Charcoal</t>
+        </is>
+      </c>
+      <c r="F32">
+        <v>6</v>
+      </c>
+      <c r="G32">
+        <v>490</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuAULIeOGtZd7vXZH0gSJHWiv3w1w4d6Tz7E7Y55Pp0wpbrudgRPkQEUxLNJ7z1iX2ofjNS4KSwbIFdzRgJR2rZEzslEi02TskRTUycOtweLNiBcTRv0RAiCUncTPXaXvHGzovAfwglQIxRlDavgkG0kp9z1__77ZtFulQa4AVlvR_muVhFSILTRpDDYMIgzrzsCEPjKJNyVc0k_NtV_qrK021aTU5RlI_Mg4TBu8JIzJLGkLHTEGfvWBezAYGbi6wNp_bgFRdeYEwST</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>AW-004</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AW-004-M</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Charcoal</t>
+        </is>
+      </c>
+      <c r="F33">
+        <v>6</v>
+      </c>
+      <c r="G33">
+        <v>490</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuAULIeOGtZd7vXZH0gSJHWiv3w1w4d6Tz7E7Y55Pp0wpbrudgRPkQEUxLNJ7z1iX2ofjNS4KSwbIFdzRgJR2rZEzslEi02TskRTUycOtweLNiBcTRv0RAiCUncTPXaXvHGzovAfwglQIxRlDavgkG0kp9z1__77ZtFulQa4AVlvR_muVhFSILTRpDDYMIgzrzsCEPjKJNyVc0k_NtV_qrK021aTU5RlI_Mg4TBu8JIzJLGkLHTEGfvWBezAYGbi6wNp_bgFRdeYEwST</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>AW-005</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AW-005-M</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Charcoal</t>
+        </is>
+      </c>
+      <c r="F34">
+        <v>8</v>
+      </c>
+      <c r="G34">
+        <v>320</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuAaOoy5mPR6kERrz2pjB05mC0JlxtRtsf2hinDbaZYFD7RKSJI_OTZn_SVo1D7JP85uSvsIZaQ5ebu77UNrwEjYJZhP6gfcKLOHkl-z5NFjTzCwUsmsvv1WbILS5HtKtmz6D5YPmeIASNcfDev_nsQcB5Odi4O5svKDuTAkJyHAlgm2j2VUKiwX_XzxOMsMjnnzRdyJcj-olztbGq4uYqe6FRhYp04lXvSqa4dkOjD9RZ1tB8UYpCw_Jj4C-Vwk4eokTl5ETem6rnWz</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>AW-005</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AW-005-L</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Charcoal</t>
+        </is>
+      </c>
+      <c r="F35">
+        <v>8</v>
+      </c>
+      <c r="G35">
+        <v>320</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuAaOoy5mPR6kERrz2pjB05mC0JlxtRtsf2hinDbaZYFD7RKSJI_OTZn_SVo1D7JP85uSvsIZaQ5ebu77UNrwEjYJZhP6gfcKLOHkl-z5NFjTzCwUsmsvv1WbILS5HtKtmz6D5YPmeIASNcfDev_nsQcB5Odi4O5svKDuTAkJyHAlgm2j2VUKiwX_XzxOMsMjnnzRdyJcj-olztbGq4uYqe6FRhYp04lXvSqa4dkOjD9RZ1tB8UYpCw_Jj4C-Vwk4eokTl5ETem6rnWz</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>AW-006</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AW-006-M</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Forest</t>
+        </is>
+      </c>
+      <c r="F36">
+        <v>5</v>
+      </c>
+      <c r="G36">
+        <v>850</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuA2sL_3eVTxv8pTPhQFFFpSQH6Kaq9or00Ox__PprWsxnH4iFcdyvkF6yE_uLy_crNRWln5sUDsqQmSo-iayh_0MyCYYTR20XSGjWAB-uNe6duE69pSu714RVSt74tQMEIF3fuTduw02xllANi1JDAtn12UeUh9ljLf8hz3xi6jPfnSdYWCX7w9y3IwSDyovmYmtsxb0x9P-3bKU5qLNiMw7cc4_t2zNEpT8QLPRQLTFIXGR2WRSQbgpFitN5ZgjO-BIsY_4Wyg7jRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>AW-006</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AW-006-L</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Forest</t>
+        </is>
+      </c>
+      <c r="F37">
+        <v>4</v>
+      </c>
+      <c r="G37">
+        <v>850</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuA2sL_3eVTxv8pTPhQFFFpSQH6Kaq9or00Ox__PprWsxnH4iFcdyvkF6yE_uLy_crNRWln5sUDsqQmSo-iayh_0MyCYYTR20XSGjWAB-uNe6duE69pSu714RVSt74tQMEIF3fuTduw02xllANi1JDAtn12UeUh9ljLf8hz3xi6jPfnSdYWCX7w9y3IwSDyovmYmtsxb0x9P-3bKU5qLNiMw7cc4_t2zNEpT8QLPRQLTFIXGR2WRSQbgpFitN5ZgjO-BIsY_4Wyg7jRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>AW-007</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AW-007-S</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Cream</t>
+        </is>
+      </c>
+      <c r="F38">
+        <v>6</v>
+      </c>
+      <c r="G38">
+        <v>410</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuBmKXEwtGPg000dRd0DYpkc78_z_0z7Q60H3fju2rnkDAllnKGSFzesSqKvn2OqncI_k-QRIvUyfVSm75I-UKw3DhxiM5eOINn4C-vJnvj2z8uKIL2AqGnXgvmqeYEEzJ5-il3zT3BTGt9iPabLxhcPbK9AwTzCM3Z9Fo3vrhfReTlHCTZ3EIgs7_JxhOFfmrNerCamtXr0QKPKlok1p5W71S8CFoXMlgrk9yrqe55hyi8oG24OwLIfOD6sAGZDuAtdrYmvQ0QD-hzg</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>AW-007</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AW-007-M</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Cream</t>
+        </is>
+      </c>
+      <c r="F39">
+        <v>5</v>
+      </c>
+      <c r="G39">
+        <v>410</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuBmKXEwtGPg000dRd0DYpkc78_z_0z7Q60H3fju2rnkDAllnKGSFzesSqKvn2OqncI_k-QRIvUyfVSm75I-UKw3DhxiM5eOINn4C-vJnvj2z8uKIL2AqGnXgvmqeYEEzJ5-il3zT3BTGt9iPabLxhcPbK9AwTzCM3Z9Fo3vrhfReTlHCTZ3EIgs7_JxhOFfmrNerCamtXr0QKPKlok1p5W71S8CFoXMlgrk9yrqe55hyi8oG24OwLIfOD6sAGZDuAtdrYmvQ0QD-hzg</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>AW-008</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AW-008-S</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Stone</t>
+        </is>
+      </c>
+      <c r="F40">
+        <v>8</v>
+      </c>
+      <c r="G40">
+        <v>295</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuBEKFEZ7Xk7Fyqc9Uf8Rr7JfhPIghhY7j0HO6bqSglckdRAUU1XFK1Vy_uPXAbpLqczXmCH41FFfT4QIgBtt7oBHhaEojRqYoMhEeW0zN9yDlgFxnnAhZfa_FjmfnZNakXUp-HAT6D2gb_BUeHA5TXBmMVsObd_AHQfOwPuMZTKrAqSkXnJe60KUnlOWajJ6btQ5zyNadwls33tVZNcDlHyJ8_EUlUAhHRtQ90ZhEzMNN5Mzjf_Hr7Onn7MZF-hkz45XkPrdm6pngSw</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>AW-008</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AW-008-M</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Stone</t>
+        </is>
+      </c>
+      <c r="F41">
+        <v>7</v>
+      </c>
+      <c r="G41">
+        <v>295</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuBEKFEZ7Xk7Fyqc9Uf8Rr7JfhPIghhY7j0HO6bqSglckdRAUU1XFK1Vy_uPXAbpLqczXmCH41FFfT4QIgBtt7oBHhaEojRqYoMhEeW0zN9yDlgFxnnAhZfa_FjmfnZNakXUp-HAT6D2gb_BUeHA5TXBmMVsObd_AHQfOwPuMZTKrAqSkXnJe60KUnlOWajJ6btQ5zyNadwls33tVZNcDlHyJ8_EUlUAhHRtQ90ZhEzMNN5Mzjf_Hr7Onn7MZF-hkz45XkPrdm6pngSw</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>AW-009</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AW-009-M</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Forest</t>
+        </is>
+      </c>
+      <c r="F42">
+        <v>3</v>
+      </c>
+      <c r="G42">
+        <v>1180</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuAULIeOGtZd7vXZH0gSJHWiv3w1w4d6Tz7E7Y55Pp0wpbrudgRPkQEUxLNJ7z1iX2ofjNS4KSwbIFdzRgJR2rZEzslEi02TskRTUycOtweLNiBcTRv0RAiCUncTPXaXvHGzovAfwglQIxRlDavgkG0kp9z1__77ZtFulQa4AVlvR_muVhFSILTRpDDYMIgzrzsCEPjKJNyVc0k_NtV_qrK021aTU5RlI_Mg4TBu8JIzJLGkLHTEGfvWBezAYGbi6wNp_bgFRdeYEwST</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>AW-009</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AW-009-L</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Forest</t>
+        </is>
+      </c>
+      <c r="F43">
+        <v>3</v>
+      </c>
+      <c r="G43">
+        <v>1180</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuAULIeOGtZd7vXZH0gSJHWiv3w1w4d6Tz7E7Y55Pp0wpbrudgRPkQEUxLNJ7z1iX2ofjNS4KSwbIFdzRgJR2rZEzslEi02TskRTUycOtweLNiBcTRv0RAiCUncTPXaXvHGzovAfwglQIxRlDavgkG0kp9z1__77ZtFulQa4AVlvR_muVhFSILTRpDDYMIgzrzsCEPjKJNyVc0k_NtV_qrK021aTU5RlI_Mg4TBu8JIzJLGkLHTEGfvWBezAYGbi6wNp_bgFRdeYEwST</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>AW-010</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AW-010-M</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Charcoal</t>
+        </is>
+      </c>
+      <c r="F44">
+        <v>7</v>
+      </c>
+      <c r="G44">
+        <v>365</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuAaOoy5mPR6kERrz2pjB05mC0JlxtRtsf2hinDbaZYFD7RKSJI_OTZn_SVo1D7JP85uSvsIZaQ5ebu77UNrwEjYJZhP6gfcKLOHkl-z5NFjTzCwUsmsvv1WbILS5HtKtmz6D5YPmeIASNcfDev_nsQcB5Odi4O5svKDuTAkJyHAlgm2j2VUKiwX_XzxOMsMjnnzRdyJcj-olztbGq4uYqe6FRhYp04lXvSqa4dkOjD9RZ1tB8UYpCw_Jj4C-Vwk4eokTl5ETem6rnWz</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>AW-010</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AW-010-L</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Charcoal</t>
+        </is>
+      </c>
+      <c r="F45">
+        <v>6</v>
+      </c>
+      <c r="G45">
+        <v>365</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuAaOoy5mPR6kERrz2pjB05mC0JlxtRtsf2hinDbaZYFD7RKSJI_OTZn_SVo1D7JP85uSvsIZaQ5ebu77UNrwEjYJZhP6gfcKLOHkl-z5NFjTzCwUsmsvv1WbILS5HtKtmz6D5YPmeIASNcfDev_nsQcB5Odi4O5svKDuTAkJyHAlgm2j2VUKiwX_XzxOMsMjnnzRdyJcj-olztbGq4uYqe6FRhYp04lXvSqa4dkOjD9RZ1tB8UYpCw_Jj4C-Vwk4eokTl5ETem6rnWz</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>AW-011</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>AW-011-XS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Cream</t>
+        </is>
+      </c>
+      <c r="F46">
+        <v>9</v>
+      </c>
+      <c r="G46">
+        <v>180</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuA2sL_3eVTxv8pTPhQFFFpSQH6Kaq9or00Ox__PprWsxnH4iFcdyvkF6yE_uLy_crNRWln5sUDsqQmSo-iayh_0MyCYYTR20XSGjWAB-uNe6duE69pSu714RVSt74tQMEIF3fuTduw02xllANi1JDAtn12UeUh9ljLf8hz3xi6jPfnSdYWCX7w9y3IwSDyovmYmtsxb0x9P-3bKU5qLNiMw7cc4_t2zNEpT8QLPRQLTFIXGR2WRSQbgpFitN5ZgjO-BIsY_4Wyg7jRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>AW-011</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AW-011-S</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Cream</t>
+        </is>
+      </c>
+      <c r="F47">
+        <v>9</v>
+      </c>
+      <c r="G47">
+        <v>180</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuA2sL_3eVTxv8pTPhQFFFpSQH6Kaq9or00Ox__PprWsxnH4iFcdyvkF6yE_uLy_crNRWln5sUDsqQmSo-iayh_0MyCYYTR20XSGjWAB-uNe6duE69pSu714RVSt74tQMEIF3fuTduw02xllANi1JDAtn12UeUh9ljLf8hz3xi6jPfnSdYWCX7w9y3IwSDyovmYmtsxb0x9P-3bKU5qLNiMw7cc4_t2zNEpT8QLPRQLTFIXGR2WRSQbgpFitN5ZgjO-BIsY_4Wyg7jRS</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>AW-012</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AW-012-S</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Stone</t>
+        </is>
+      </c>
+      <c r="F48">
+        <v>5</v>
+      </c>
+      <c r="G48">
+        <v>430</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuBmKXEwtGPg000dRd0DYpkc78_z_0z7Q60H3fju2rnkDAllnKGSFzesSqKvn2OqncI_k-QRIvUyfVSm75I-UKw3DhxiM5eOINn4C-vJnvj2z8uKIL2AqGnXgvmqeYEEzJ5-il3zT3BTGt9iPabLxhcPbK9AwTzCM3Z9Fo3vrhfReTlHCTZ3EIgs7_JxhOFfmrNerCamtXr0QKPKlok1p5W71S8CFoXMlgrk9yrqe55hyi8oG24OwLIfOD6sAGZDuAtdrYmvQ0QD-hzg</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>AW-012</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AW-012-M</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Stone</t>
+        </is>
+      </c>
+      <c r="F49">
+        <v>5</v>
+      </c>
+      <c r="G49">
+        <v>430</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuBmKXEwtGPg000dRd0DYpkc78_z_0z7Q60H3fju2rnkDAllnKGSFzesSqKvn2OqncI_k-QRIvUyfVSm75I-UKw3DhxiM5eOINn4C-vJnvj2z8uKIL2AqGnXgvmqeYEEzJ5-il3zT3BTGt9iPabLxhcPbK9AwTzCM3Z9Fo3vrhfReTlHCTZ3EIgs7_JxhOFfmrNerCamtXr0QKPKlok1p5W71S8CFoXMlgrk9yrqe55hyi8oG24OwLIfOD6sAGZDuAtdrYmvQ0QD-hzg</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>FW-001</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>FW-001-40</t>
+        </is>
+      </c>
+      <c r="D50">
+        <v>40</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Chalk</t>
+        </is>
+      </c>
+      <c r="F50">
+        <v>9</v>
+      </c>
+      <c r="G50">
+        <v>340</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuAMYKBjYQhfEPiX1rrzGJqP-bZ3N-za3aIYrq4ZJ7iHUOBBELUJUpvBk3Ms1bHaAXBuEZwTIczKGpjLz2AbAXSyAma0h_FRPa4MA_RgE9EO-SCavieX4XPDLcnuloZs8tAGD5FGHlcBtSszlVWYz-FA-hca0gi-xkAC4k_vrZmULdCAPQNXUhSbE3wrhj8_XgthXU6Aso4ltg4ME3nEgOsgEaBDUB6hKvQ_Ere_31vsZ98zkTq0zGrgjNqUJHCDPBUQPmqG9Q702KKw</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>FW-001</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>FW-001-41</t>
+        </is>
+      </c>
+      <c r="D51">
+        <v>41</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Chalk</t>
+        </is>
+      </c>
+      <c r="F51">
+        <v>9</v>
+      </c>
+      <c r="G51">
+        <v>340</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuAMYKBjYQhfEPiX1rrzGJqP-bZ3N-za3aIYrq4ZJ7iHUOBBELUJUpvBk3Ms1bHaAXBuEZwTIczKGpjLz2AbAXSyAma0h_FRPa4MA_RgE9EO-SCavieX4XPDLcnuloZs8tAGD5FGHlcBtSszlVWYz-FA-hca0gi-xkAC4k_vrZmULdCAPQNXUhSbE3wrhj8_XgthXU6Aso4ltg4ME3nEgOsgEaBDUB6hKvQ_Ere_31vsZ98zkTq0zGrgjNqUJHCDPBUQPmqG9Q702KKw</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>FW-002</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>FW-002-41</t>
+        </is>
+      </c>
+      <c r="D52">
+        <v>41</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Cedar</t>
+        </is>
+      </c>
+      <c r="F52">
+        <v>6</v>
+      </c>
+      <c r="G52">
+        <v>495</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuD5KVhgLop51bisay_zrsW8YVtKdD2et-udRx64dbQtp0xYp4CE38R94dLqJO460aolSqy9UdPhfvdjSyjzz7Bbh4MOeBkHbehqlMCTvPNv4PLXn3wFu6XqNIM_5UyUXX71NRni2ntQt4twbRrDvUPUi5cDXb-939ibHoOeSHMsDghYNOy7kZp5gd14kjIf6WUveYq0O9RFsuf5oY9RK1U9jhhlcJ_HJPXAwSBdNK2y67FH0n0MdcVNPoEwpIxvSAkUOZdh9YgdL7FA</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>FW-002</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>FW-002-42</t>
+        </is>
+      </c>
+      <c r="D53">
         <v>42</v>
       </c>
-      <c r="G4">
-        <v>49.99</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>https://example.com/images/sm002-s.jpg</t>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Cedar</t>
+        </is>
+      </c>
+      <c r="F53">
+        <v>5</v>
+      </c>
+      <c r="G53">
+        <v>495</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuD5KVhgLop51bisay_zrsW8YVtKdD2et-udRx64dbQtp0xYp4CE38R94dLqJO460aolSqy9UdPhfvdjSyjzz7Bbh4MOeBkHbehqlMCTvPNv4PLXn3wFu6XqNIM_5UyUXX71NRni2ntQt4twbRrDvUPUi5cDXb-939ibHoOeSHMsDghYNOy7kZp5gd14kjIf6WUveYq0O9RFsuf5oY9RK1U9jhhlcJ_HJPXAwSBdNK2y67FH0n0MdcVNPoEwpIxvSAkUOZdh9YgdL7FA</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>FW-003</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>FW-003-40</t>
+        </is>
+      </c>
+      <c r="D54">
+        <v>40</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="F54">
+        <v>6</v>
+      </c>
+      <c r="G54">
+        <v>420</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuAAhJretAaN4nn0hwa-S3geRVjspqi5Iysp4o9wJ6Umsp05BfiGqmXjoyIkxI-iO9bJQHh6aFW1ByRoH4hP6tAQ1ifpRkG88XfFjHc7Tu8bEt310kgkBdS8l4wXyGN477geZFXoBXA7tpLWEx-ySFm69csgvDnFB-DbTmu1Va59aScYOFNkVt4WimRi19ZpDNf2YvhkDC8ETmf7ZpivWgg0fG1e-5cX386ZaOUDjcQ35GqrXeknlGJ-ig73LknVdiR_VbQ_rfBrjtto</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>FW-003</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>FW-003-41</t>
+        </is>
+      </c>
+      <c r="D55">
+        <v>41</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="F55">
+        <v>6</v>
+      </c>
+      <c r="G55">
+        <v>420</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuAAhJretAaN4nn0hwa-S3geRVjspqi5Iysp4o9wJ6Umsp05BfiGqmXjoyIkxI-iO9bJQHh6aFW1ByRoH4hP6tAQ1ifpRkG88XfFjHc7Tu8bEt310kgkBdS8l4wXyGN477geZFXoBXA7tpLWEx-ySFm69csgvDnFB-DbTmu1Va59aScYOFNkVt4WimRi19ZpDNf2YvhkDC8ETmf7ZpivWgg0fG1e-5cX386ZaOUDjcQ35GqrXeknlGJ-ig73LknVdiR_VbQ_rfBrjtto</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>FW-004</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>FW-004-42</t>
+        </is>
+      </c>
+      <c r="D56">
+        <v>42</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Tobacco</t>
+        </is>
+      </c>
+      <c r="F56">
+        <v>5</v>
+      </c>
+      <c r="G56">
+        <v>560</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuD4G3y0ZNdrqZS0ATojfSYa5t42Vrrx476FUX5qzvdCm_CCtF0C5yrINsDw4_G71jrBcMmaoueccHcMXO1xws91KQPeOyvLKzB9nAJZ70r7sO7YUn_u5DMqM93aUESLHoGVqBzejgzYA6j31SfDmrQl3IeBeL-xTBwhgq4AG_zSgROd0lwpbM9okRm26Hm2PbSk7bsL6aFYLo561VTjxiVDA_m28FuAt2wvBZpwLQNP23z7cESJyuNoMgdIyfHRBsZerL9BQbZ5D2p1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>FW-004</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>FW-004-43</t>
+        </is>
+      </c>
+      <c r="D57">
+        <v>43</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Tobacco</t>
+        </is>
+      </c>
+      <c r="F57">
+        <v>4</v>
+      </c>
+      <c r="G57">
+        <v>560</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuD4G3y0ZNdrqZS0ATojfSYa5t42Vrrx476FUX5qzvdCm_CCtF0C5yrINsDw4_G71jrBcMmaoueccHcMXO1xws91KQPeOyvLKzB9nAJZ70r7sO7YUn_u5DMqM93aUESLHoGVqBzejgzYA6j31SfDmrQl3IeBeL-xTBwhgq4AG_zSgROd0lwpbM9okRm26Hm2PbSk7bsL6aFYLo561VTjxiVDA_m28FuAt2wvBZpwLQNP23z7cESJyuNoMgdIyfHRBsZerL9BQbZ5D2p1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>FW-005</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>FW-005-42</t>
+        </is>
+      </c>
+      <c r="D58">
+        <v>42</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Walnut</t>
+        </is>
+      </c>
+      <c r="F58">
+        <v>4</v>
+      </c>
+      <c r="G58">
+        <v>610</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuAMYKBjYQhfEPiX1rrzGJqP-bZ3N-za3aIYrq4ZJ7iHUOBBELUJUpvBk3Ms1bHaAXBuEZwTIczKGpjLz2AbAXSyAma0h_FRPa4MA_RgE9EO-SCavieX4XPDLcnuloZs8tAGD5FGHlcBtSszlVWYz-FA-hca0gi-xkAC4k_vrZmULdCAPQNXUhSbE3wrhj8_XgthXU6Aso4ltg4ME3nEgOsgEaBDUB6hKvQ_Ere_31vsZ98zkTq0zGrgjNqUJHCDPBUQPmqG9Q702KKw</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>FW-005</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>FW-005-43</t>
+        </is>
+      </c>
+      <c r="D59">
+        <v>43</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Walnut</t>
+        </is>
+      </c>
+      <c r="F59">
+        <v>4</v>
+      </c>
+      <c r="G59">
+        <v>610</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuAMYKBjYQhfEPiX1rrzGJqP-bZ3N-za3aIYrq4ZJ7iHUOBBELUJUpvBk3Ms1bHaAXBuEZwTIczKGpjLz2AbAXSyAma0h_FRPa4MA_RgE9EO-SCavieX4XPDLcnuloZs8tAGD5FGHlcBtSszlVWYz-FA-hca0gi-xkAC4k_vrZmULdCAPQNXUhSbE3wrhj8_XgthXU6Aso4ltg4ME3nEgOsgEaBDUB6hKvQ_Ere_31vsZ98zkTq0zGrgjNqUJHCDPBUQPmqG9Q702KKw</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>FW-006</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>FW-006-40</t>
+        </is>
+      </c>
+      <c r="D60">
+        <v>40</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Espresso</t>
+        </is>
+      </c>
+      <c r="F60">
+        <v>5</v>
+      </c>
+      <c r="G60">
+        <v>450</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuD5KVhgLop51bisay_zrsW8YVtKdD2et-udRx64dbQtp0xYp4CE38R94dLqJO460aolSqy9UdPhfvdjSyjzz7Bbh4MOeBkHbehqlMCTvPNv4PLXn3wFu6XqNIM_5UyUXX71NRni2ntQt4twbRrDvUPUi5cDXb-939ibHoOeSHMsDghYNOy7kZp5gd14kjIf6WUveYq0O9RFsuf5oY9RK1U9jhhlcJ_HJPXAwSBdNK2y67FH0n0MdcVNPoEwpIxvSAkUOZdh9YgdL7FA</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>FW-006</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>FW-006-41</t>
+        </is>
+      </c>
+      <c r="D61">
+        <v>41</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Espresso</t>
+        </is>
+      </c>
+      <c r="F61">
+        <v>5</v>
+      </c>
+      <c r="G61">
+        <v>450</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuD5KVhgLop51bisay_zrsW8YVtKdD2et-udRx64dbQtp0xYp4CE38R94dLqJO460aolSqy9UdPhfvdjSyjzz7Bbh4MOeBkHbehqlMCTvPNv4PLXn3wFu6XqNIM_5UyUXX71NRni2ntQt4twbRrDvUPUi5cDXb-939ibHoOeSHMsDghYNOy7kZp5gd14kjIf6WUveYq0O9RFsuf5oY9RK1U9jhhlcJ_HJPXAwSBdNK2y67FH0n0MdcVNPoEwpIxvSAkUOZdh9YgdL7FA</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>FW-007</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>FW-007-41</t>
+        </is>
+      </c>
+      <c r="D62">
+        <v>41</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Slate</t>
+        </is>
+      </c>
+      <c r="F62">
+        <v>5</v>
+      </c>
+      <c r="G62">
+        <v>470</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuAAhJretAaN4nn0hwa-S3geRVjspqi5Iysp4o9wJ6Umsp05BfiGqmXjoyIkxI-iO9bJQHh6aFW1ByRoH4hP6tAQ1ifpRkG88XfFjHc7Tu8bEt310kgkBdS8l4wXyGN477geZFXoBXA7tpLWEx-ySFm69csgvDnFB-DbTmu1Va59aScYOFNkVt4WimRi19ZpDNf2YvhkDC8ETmf7ZpivWgg0fG1e-5cX386ZaOUDjcQ35GqrXeknlGJ-ig73LknVdiR_VbQ_rfBrjtto</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>FW-007</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>FW-007-42</t>
+        </is>
+      </c>
+      <c r="D63">
+        <v>42</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Slate</t>
+        </is>
+      </c>
+      <c r="F63">
+        <v>5</v>
+      </c>
+      <c r="G63">
+        <v>470</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuAAhJretAaN4nn0hwa-S3geRVjspqi5Iysp4o9wJ6Umsp05BfiGqmXjoyIkxI-iO9bJQHh6aFW1ByRoH4hP6tAQ1ifpRkG88XfFjHc7Tu8bEt310kgkBdS8l4wXyGN477geZFXoBXA7tpLWEx-ySFm69csgvDnFB-DbTmu1Va59aScYOFNkVt4WimRi19ZpDNf2YvhkDC8ETmf7ZpivWgg0fG1e-5cX386ZaOUDjcQ35GqrXeknlGJ-ig73LknVdiR_VbQ_rfBrjtto</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>FW-008</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>FW-008-40</t>
+        </is>
+      </c>
+      <c r="D64">
+        <v>40</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Bone</t>
+        </is>
+      </c>
+      <c r="F64">
+        <v>8</v>
+      </c>
+      <c r="G64">
+        <v>360</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuD4G3y0ZNdrqZS0ATojfSYa5t42Vrrx476FUX5qzvdCm_CCtF0C5yrINsDw4_G71jrBcMmaoueccHcMXO1xws91KQPeOyvLKzB9nAJZ70r7sO7YUn_u5DMqM93aUESLHoGVqBzejgzYA6j31SfDmrQl3IeBeL-xTBwhgq4AG_zSgROd0lwpbM9okRm26Hm2PbSk7bsL6aFYLo561VTjxiVDA_m28FuAt2wvBZpwLQNP23z7cESJyuNoMgdIyfHRBsZerL9BQbZ5D2p1</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>FW-008</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>FW-008-41</t>
+        </is>
+      </c>
+      <c r="D65">
+        <v>41</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Bone</t>
+        </is>
+      </c>
+      <c r="F65">
+        <v>8</v>
+      </c>
+      <c r="G65">
+        <v>360</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuD4G3y0ZNdrqZS0ATojfSYa5t42Vrrx476FUX5qzvdCm_CCtF0C5yrINsDw4_G71jrBcMmaoueccHcMXO1xws91KQPeOyvLKzB9nAJZ70r7sO7YUn_u5DMqM93aUESLHoGVqBzejgzYA6j31SfDmrQl3IeBeL-xTBwhgq4AG_zSgROd0lwpbM9okRm26Hm2PbSk7bsL6aFYLo561VTjxiVDA_m28FuAt2wvBZpwLQNP23z7cESJyuNoMgdIyfHRBsZerL9BQbZ5D2p1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>FW-009</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>FW-009-41</t>
+        </is>
+      </c>
+      <c r="D66">
+        <v>41</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Mahogany</t>
+        </is>
+      </c>
+      <c r="F66">
+        <v>4</v>
+      </c>
+      <c r="G66">
+        <v>530</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuAMYKBjYQhfEPiX1rrzGJqP-bZ3N-za3aIYrq4ZJ7iHUOBBELUJUpvBk3Ms1bHaAXBuEZwTIczKGpjLz2AbAXSyAma0h_FRPa4MA_RgE9EO-SCavieX4XPDLcnuloZs8tAGD5FGHlcBtSszlVWYz-FA-hca0gi-xkAC4k_vrZmULdCAPQNXUhSbE3wrhj8_XgthXU6Aso4ltg4ME3nEgOsgEaBDUB6hKvQ_Ere_31vsZ98zkTq0zGrgjNqUJHCDPBUQPmqG9Q702KKw</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>FW-009</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>FW-009-42</t>
+        </is>
+      </c>
+      <c r="D67">
+        <v>42</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Mahogany</t>
+        </is>
+      </c>
+      <c r="F67">
+        <v>3</v>
+      </c>
+      <c r="G67">
+        <v>530</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuAMYKBjYQhfEPiX1rrzGJqP-bZ3N-za3aIYrq4ZJ7iHUOBBELUJUpvBk3Ms1bHaAXBuEZwTIczKGpjLz2AbAXSyAma0h_FRPa4MA_RgE9EO-SCavieX4XPDLcnuloZs8tAGD5FGHlcBtSszlVWYz-FA-hca0gi-xkAC4k_vrZmULdCAPQNXUhSbE3wrhj8_XgthXU6Aso4ltg4ME3nEgOsgEaBDUB6hKvQ_Ere_31vsZ98zkTq0zGrgjNqUJHCDPBUQPmqG9Q702KKw</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000067</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>FW-010</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>FW-010-40</t>
+        </is>
+      </c>
+      <c r="D68">
+        <v>40</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Taupe</t>
+        </is>
+      </c>
+      <c r="F68">
+        <v>6</v>
+      </c>
+      <c r="G68">
+        <v>390</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuD5KVhgLop51bisay_zrsW8YVtKdD2et-udRx64dbQtp0xYp4CE38R94dLqJO460aolSqy9UdPhfvdjSyjzz7Bbh4MOeBkHbehqlMCTvPNv4PLXn3wFu6XqNIM_5UyUXX71NRni2ntQt4twbRrDvUPUi5cDXb-939ibHoOeSHMsDghYNOy7kZp5gd14kjIf6WUveYq0O9RFsuf5oY9RK1U9jhhlcJ_HJPXAwSBdNK2y67FH0n0MdcVNPoEwpIxvSAkUOZdh9YgdL7FA</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000068</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>FW-010</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>FW-010-41</t>
+        </is>
+      </c>
+      <c r="D69">
+        <v>41</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Taupe</t>
+        </is>
+      </c>
+      <c r="F69">
+        <v>6</v>
+      </c>
+      <c r="G69">
+        <v>390</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuD5KVhgLop51bisay_zrsW8YVtKdD2et-udRx64dbQtp0xYp4CE38R94dLqJO460aolSqy9UdPhfvdjSyjzz7Bbh4MOeBkHbehqlMCTvPNv4PLXn3wFu6XqNIM_5UyUXX71NRni2ntQt4twbRrDvUPUi5cDXb-939ibHoOeSHMsDghYNOy7kZp5gd14kjIf6WUveYq0O9RFsuf5oY9RK1U9jhhlcJ_HJPXAwSBdNK2y67FH0n0MdcVNPoEwpIxvSAkUOZdh9YgdL7FA</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000069</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>FW-011</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>FW-011-39</t>
+        </is>
+      </c>
+      <c r="D70">
+        <v>39</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Sand</t>
+        </is>
+      </c>
+      <c r="F70">
+        <v>7</v>
+      </c>
+      <c r="G70">
+        <v>310</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuAAhJretAaN4nn0hwa-S3geRVjspqi5Iysp4o9wJ6Umsp05BfiGqmXjoyIkxI-iO9bJQHh6aFW1ByRoH4hP6tAQ1ifpRkG88XfFjHc7Tu8bEt310kgkBdS8l4wXyGN477geZFXoBXA7tpLWEx-ySFm69csgvDnFB-DbTmu1Va59aScYOFNkVt4WimRi19ZpDNf2YvhkDC8ETmf7ZpivWgg0fG1e-5cX386ZaOUDjcQ35GqrXeknlGJ-ig73LknVdiR_VbQ_rfBrjtto</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>FW-011</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>FW-011-40</t>
+        </is>
+      </c>
+      <c r="D71">
+        <v>40</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Sand</t>
+        </is>
+      </c>
+      <c r="F71">
+        <v>7</v>
+      </c>
+      <c r="G71">
+        <v>310</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuAAhJretAaN4nn0hwa-S3geRVjspqi5Iysp4o9wJ6Umsp05BfiGqmXjoyIkxI-iO9bJQHh6aFW1ByRoH4hP6tAQ1ifpRkG88XfFjHc7Tu8bEt310kgkBdS8l4wXyGN477geZFXoBXA7tpLWEx-ySFm69csgvDnFB-DbTmu1Va59aScYOFNkVt4WimRi19ZpDNf2YvhkDC8ETmf7ZpivWgg0fG1e-5cX386ZaOUDjcQ35GqrXeknlGJ-ig73LknVdiR_VbQ_rfBrjtto</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000071</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>FW-012</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>FW-012-42</t>
+        </is>
+      </c>
+      <c r="D72">
+        <v>42</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="F72">
+        <v>4</v>
+      </c>
+      <c r="G72">
+        <v>580</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuD4G3y0ZNdrqZS0ATojfSYa5t42Vrrx476FUX5qzvdCm_CCtF0C5yrINsDw4_G71jrBcMmaoueccHcMXO1xws91KQPeOyvLKzB9nAJZ70r7sO7YUn_u5DMqM93aUESLHoGVqBzejgzYA6j31SfDmrQl3IeBeL-xTBwhgq4AG_zSgROd0lwpbM9okRm26Hm2PbSk7bsL6aFYLo561VTjxiVDA_m28FuAt2wvBZpwLQNP23z7cESJyuNoMgdIyfHRBsZerL9BQbZ5D2p1</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000072</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>FW-012</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>FW-012-43</t>
+        </is>
+      </c>
+      <c r="D73">
+        <v>43</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="F73">
+        <v>4</v>
+      </c>
+      <c r="G73">
+        <v>580</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuD4G3y0ZNdrqZS0ATojfSYa5t42Vrrx476FUX5qzvdCm_CCtF0C5yrINsDw4_G71jrBcMmaoueccHcMXO1xws91KQPeOyvLKzB9nAJZ70r7sO7YUn_u5DMqM93aUESLHoGVqBzejgzYA6j31SfDmrQl3IeBeL-xTBwhgq4AG_zSgROd0lwpbM9okRm26Hm2PbSk7bsL6aFYLo561VTjxiVDA_m28FuAt2wvBZpwLQNP23z7cESJyuNoMgdIyfHRBsZerL9BQbZ5D2p1</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000073</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>AC-001</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>AC-001-OS</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Forest</t>
+        </is>
+      </c>
+      <c r="F74">
+        <v>9</v>
+      </c>
+      <c r="G74">
+        <v>840</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuBBESdqWOWSR5qEzSZhDSiYksfl92Z2-nXfieKv7zls3FB-7JuZVx-N6rXRCgkpMkJyxFCIzvAJAfUETLq2m7IDhOFmOtlLXZ9qEspJxSM3dIgXBbd3dzVswFhn3Y0MqayyDJYGSylH-MIjZnLLMaswkecd7-JUIltIP_szY3CTjkboRukxyb0Hicjh_fTS7Q8NRXCPfvyi2Gd8UjbveWvWIIUauI-d4h0ra0W790prCr-I9666OBdQ8zWwoQM8OSo6iYMbifIvLw2n</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000074</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>AC-002</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>AC-002-OS</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Sand</t>
+        </is>
+      </c>
+      <c r="F75">
+        <v>18</v>
+      </c>
+      <c r="G75">
+        <v>215</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuCJ_mIoxtuOYX0UmZ6fp1vpG_etnXOkuxN0sOW8aXUVddHj5eDEGxKoK_oij-8jI8EDqrG_IXPuR5HXX_5FgjnVIMXKR3rvffkz_2hI2uHpAzMIbNZASVlBgA47Ecvrg53PTIsx8zim-xN9ZKFMoR3ivhIQDQ1jUJ0fFx2scgrGApYeeDOx-irk-VfW38VMHIZ4QMUtn6sXwUjEJRXtZ8dTLBnKQVPGxBzf7oOFEbYGY_2P__2xLjofQjJvPkwrIzkn9OjMEUgKEC2O</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000075</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>AC-003</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>AC-003-S</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Tobacco</t>
+        </is>
+      </c>
+      <c r="F76">
+        <v>10</v>
+      </c>
+      <c r="G76">
+        <v>165</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuDclyoI7lW_Aez2lBayMz4ES5BVdH-wo43IL4ZwpD4HLQkaJqfV3eDM-qMUs4V8Uyl6BTZ9FSNg7ExFisE6J-TMxcflCy5mFritcP54bDT49eqwGnwGnsOeheOgbCmpdtfGvnHaqpfmRpU4zQvBD7B4tmigGgv7hCDEHWLojIzOlAfe5p-0cCnzLjktClPIw5lG6h2qfT0buVNcsY57FFriSrjdMpV_jPcwn3Dwsz1C-8IS20dhOYE1-Kak6Hi0R-OiEeULdIqMBj2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000076</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>AC-003</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>AC-003-M</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Tobacco</t>
+        </is>
+      </c>
+      <c r="F77">
+        <v>10</v>
+      </c>
+      <c r="G77">
+        <v>165</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuDclyoI7lW_Aez2lBayMz4ES5BVdH-wo43IL4ZwpD4HLQkaJqfV3eDM-qMUs4V8Uyl6BTZ9FSNg7ExFisE6J-TMxcflCy5mFritcP54bDT49eqwGnwGnsOeheOgbCmpdtfGvnHaqpfmRpU4zQvBD7B4tmigGgv7hCDEHWLojIzOlAfe5p-0cCnzLjktClPIw5lG6h2qfT0buVNcsY57FFriSrjdMpV_jPcwn3Dwsz1C-8IS20dhOYE1-Kak6Hi0R-OiEeULdIqMBj2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000077</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>AC-004</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>AC-004-OS</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Cognac</t>
+        </is>
+      </c>
+      <c r="F78">
+        <v>10</v>
+      </c>
+      <c r="G78">
+        <v>420</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuAc-xgefZmjRHW4tYawNPs3ljWfgQ66YMBuFgX39XflOo-rQyjbJ2Ju2V0nLkyj2SVuz2BKsp1ucM74P4Gg2Q-TiJKsqrjsQRpxYORvaVExN0KFMkAU9KQFmWEmtNZHK5dm7iBBb1zYMTsluHO4Em5IwIi3lS3JGSUeU_unqmYgh-Fw65tcUaH2Ywxl8ag7h1znu1rGefQrkuDTARLHNwtQdpiGPKWCCp8JpO_yLO4kKGzLmwj8g3VfRzxs02GzkmBt2St6l1zyFYZU</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000078</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>AC-005</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>AC-005-M</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="F79">
+        <v>6</v>
+      </c>
+      <c r="G79">
+        <v>310</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuDwib-yVKWuTMsi4heheiLMLuw3Aukcrj4t8F5TLsWcUDULrkliTF_b5hFcyekqcaoBOrRCOob6yU3tV5aJCQChHBAggBedojt1THWZ_F-1GiBclBPJw389BrO0MvSA5xrOo1ssievm9rXO2UiIT0Ix_tHvr6rnGAPSAVNt1DYmLJVg_7vuvdan2zI6d3Z7JsuFwAqcipqjdi0FbCpFwqD4d7bZrq5JeL4i4aGx5NsOkOBZScx3UPHkR_rmJldHJi3Cb4MoiZaIoNsN</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000079</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>AC-005</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>AC-005-L</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="F80">
+        <v>6</v>
+      </c>
+      <c r="G80">
+        <v>310</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuDwib-yVKWuTMsi4heheiLMLuw3Aukcrj4t8F5TLsWcUDULrkliTF_b5hFcyekqcaoBOrRCOob6yU3tV5aJCQChHBAggBedojt1THWZ_F-1GiBclBPJw389BrO0MvSA5xrOo1ssievm9rXO2UiIT0Ix_tHvr6rnGAPSAVNt1DYmLJVg_7vuvdan2zI6d3Z7JsuFwAqcipqjdi0FbCpFwqD4d7bZrq5JeL4i4aGx5NsOkOBZScx3UPHkR_rmJldHJi3Cb4MoiZaIoNsN</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>AC-006</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>AC-006-OS</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Mist</t>
+        </is>
+      </c>
+      <c r="F81">
+        <v>16</v>
+      </c>
+      <c r="G81">
+        <v>190</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuBBESdqWOWSR5qEzSZhDSiYksfl92Z2-nXfieKv7zls3FB-7JuZVx-N6rXRCgkpMkJyxFCIzvAJAfUETLq2m7IDhOFmOtlLXZ9qEspJxSM3dIgXBbd3dzVswFhn3Y0MqayyDJYGSylH-MIjZnLLMaswkecd7-JUIltIP_szY3CTjkboRukxyb0Hicjh_fTS7Q8NRXCPfvyi2Gd8UjbveWvWIIUauI-d4h0ra0W790prCr-I9666OBdQ8zWwoQM8OSo6iYMbifIvLw2n</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000081</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>AC-007</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>AC-007-OS</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Espresso</t>
+        </is>
+      </c>
+      <c r="F82">
+        <v>7</v>
+      </c>
+      <c r="G82">
+        <v>980</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuCJ_mIoxtuOYX0UmZ6fp1vpG_etnXOkuxN0sOW8aXUVddHj5eDEGxKoK_oij-8jI8EDqrG_IXPuR5HXX_5FgjnVIMXKR3rvffkz_2hI2uHpAzMIbNZASVlBgA47Ecvrg53PTIsx8zim-xN9ZKFMoR3ivhIQDQ1jUJ0fFx2scgrGApYeeDOx-irk-VfW38VMHIZ4QMUtn6sXwUjEJRXtZ8dTLBnKQVPGxBzf7oOFEbYGY_2P__2xLjofQjJvPkwrIzkn9OjMEUgKEC2O</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000082</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>AC-008</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>AC-008-OS</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="F83">
+        <v>15</v>
+      </c>
+      <c r="G83">
+        <v>145</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuDclyoI7lW_Aez2lBayMz4ES5BVdH-wo43IL4ZwpD4HLQkaJqfV3eDM-qMUs4V8Uyl6BTZ9FSNg7ExFisE6J-TMxcflCy5mFritcP54bDT49eqwGnwGnsOeheOgbCmpdtfGvnHaqpfmRpU4zQvBD7B4tmigGgv7hCDEHWLojIzOlAfe5p-0cCnzLjktClPIw5lG6h2qfT0buVNcsY57FFriSrjdMpV_jPcwn3Dwsz1C-8IS20dhOYE1-Kak6Hi0R-OiEeULdIqMBj2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000083</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>AC-009</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>AC-009-OS</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Tan</t>
+        </is>
+      </c>
+      <c r="F84">
+        <v>14</v>
+      </c>
+      <c r="G84">
+        <v>110</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuAc-xgefZmjRHW4tYawNPs3ljWfgQ66YMBuFgX39XflOo-rQyjbJ2Ju2V0nLkyj2SVuz2BKsp1ucM74P4Gg2Q-TiJKsqrjsQRpxYORvaVExN0KFMkAU9KQFmWEmtNZHK5dm7iBBb1zYMTsluHO4Em5IwIi3lS3JGSUeU_unqmYgh-Fw65tcUaH2Ywxl8ag7h1znu1rGefQrkuDTARLHNwtQdpiGPKWCCp8JpO_yLO4kKGzLmwj8g3VfRzxs02GzkmBt2St6l1zyFYZU</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000084</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>AC-010</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>AC-010-OS</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Pearl</t>
+        </is>
+      </c>
+      <c r="F85">
+        <v>17</v>
+      </c>
+      <c r="G85">
+        <v>175</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuDwib-yVKWuTMsi4heheiLMLuw3Aukcrj4t8F5TLsWcUDULrkliTF_b5hFcyekqcaoBOrRCOob6yU3tV5aJCQChHBAggBedojt1THWZ_F-1GiBclBPJw389BrO0MvSA5xrOo1ssievm9rXO2UiIT0Ix_tHvr6rnGAPSAVNt1DYmLJVg_7vuvdan2zI6d3Z7JsuFwAqcipqjdi0FbCpFwqD4d7bZrq5JeL4i4aGx5NsOkOBZScx3UPHkR_rmJldHJi3Cb4MoiZaIoNsN</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000085</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>AC-011</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>AC-011-M</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="F86">
+        <v>6</v>
+      </c>
+      <c r="G86">
+        <v>265</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuBBESdqWOWSR5qEzSZhDSiYksfl92Z2-nXfieKv7zls3FB-7JuZVx-N6rXRCgkpMkJyxFCIzvAJAfUETLq2m7IDhOFmOtlLXZ9qEspJxSM3dIgXBbd3dzVswFhn3Y0MqayyDJYGSylH-MIjZnLLMaswkecd7-JUIltIP_szY3CTjkboRukxyb0Hicjh_fTS7Q8NRXCPfvyi2Gd8UjbveWvWIIUauI-d4h0ra0W790prCr-I9666OBdQ8zWwoQM8OSo6iYMbifIvLw2n</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000086</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>AC-011</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>AC-011-L</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="F87">
+        <v>5</v>
+      </c>
+      <c r="G87">
+        <v>265</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuBBESdqWOWSR5qEzSZhDSiYksfl92Z2-nXfieKv7zls3FB-7JuZVx-N6rXRCgkpMkJyxFCIzvAJAfUETLq2m7IDhOFmOtlLXZ9qEspJxSM3dIgXBbd3dzVswFhn3Y0MqayyDJYGSylH-MIjZnLLMaswkecd7-JUIltIP_szY3CTjkboRukxyb0Hicjh_fTS7Q8NRXCPfvyi2Gd8UjbveWvWIIUauI-d4h0ra0W790prCr-I9666OBdQ8zWwoQM8OSo6iYMbifIvLw2n</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>20000000-0000-4000-8000-000000000087</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>AC-012</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>AC-012-OS</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Taupe</t>
+        </is>
+      </c>
+      <c r="F88">
+        <v>9</v>
+      </c>
+      <c r="G88">
+        <v>390</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://lh3.googleusercontent.com/aida-public/AB6AXuCJ_mIoxtuOYX0UmZ6fp1vpG_etnXOkuxN0sOW8aXUVddHj5eDEGxKoK_oij-8jI8EDqrG_IXPuR5HXX_5FgjnVIMXKR3rvffkz_2hI2uHpAzMIbNZASVlBgA47Ecvrg53PTIsx8zim-xN9ZKFMoR3ivhIQDQ1jUJ0fFx2scgrGApYeeDOx-irk-VfW38VMHIZ4QMUtn6sXwUjEJRXtZ8dTLBnKQVPGxBzf7oOFEbYGY_2P__2xLjofQjJvPkwrIzkn9OjMEUgKEC2O</t>
         </is>
       </c>
     </row>
@@ -650,7 +6162,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -688,7 +6200,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>770e8400-e29b-41d4-a716-446655440000</t>
+          <t>30000000-0000-4000-8000-000000000001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -706,7 +6218,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>{"variant":"dark-immersive","title":"Spring Drop","subtitle":"New arrivals"}</t>
+          <t>{"variant":"dark-immersive","title":"Structured Essentials","subtitle":"Twelve menswear products seeded for local catalog demos."}</t>
         </is>
       </c>
       <c r="F2" t="b">
@@ -716,7 +6228,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>770e8400-e29b-41d4-a716-446655440001</t>
+          <t>30000000-0000-4000-8000-000000000002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -734,7 +6246,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>{"columns":3,"productIds":["SM-001","SM-002"]}</t>
+          <t>{"columns":4,"productIds":["SM-001","SM-002","SM-003","SM-004","SM-005","SM-006"]}</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -744,28 +6256,280 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>770e8400-e29b-41d4-a716-446655440002</t>
+          <t>30000000-0000-4000-8000-000000000003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>shop-men</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>story-block</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>{"heading":"Material Study","body":"Dense wool, washed linen, and refined cotton give the men's sample catalog a sharper backbone."}</t>
+        </is>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>30000000-0000-4000-8000-000000000004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>atelier-women</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>hero-banner</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>{"variant":"light-editorial","title":"Quiet Luxury Pieces","subtitle":"Twelve women's products seeded for local editorial demos."}</t>
+        </is>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>30000000-0000-4000-8000-000000000005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>atelier-women</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>product-grid</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>{"columns":4,"productIds":["AW-001","AW-002","AW-003","AW-004","AW-005","AW-006"]}</t>
+        </is>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>30000000-0000-4000-8000-000000000006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>atelier-women</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>story-block</t>
         </is>
       </c>
-      <c r="D4">
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>{"heading":"Soft Structure","body":"Fluid dresses, sculptural coats, and richer knit textures define the women's sample catalog."}</t>
+        </is>
+      </c>
+      <c r="F7" t="b">
         <v>1</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>{"heading":"Craftsmanship","body":"Hand-stitched details"}</t>
-        </is>
-      </c>
-      <c r="F4" t="b">
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>30000000-0000-4000-8000-000000000007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>hero-banner</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>{"variant":"workshop-editorial","title":"Workshop Built","subtitle":"Twelve footwear products seeded for local catalog demos."}</t>
+        </is>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>30000000-0000-4000-8000-000000000008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>product-grid</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>{"columns":4,"productIds":["FW-001","FW-002","FW-003","FW-004","FW-005","FW-006"]}</t>
+        </is>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>30000000-0000-4000-8000-000000000009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>story-block</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>{"heading":"Craft &amp; Hardware","body":"Edge finishing, leather character, and durable hardware shape the footwear sample catalog."}</t>
+        </is>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>30000000-0000-4000-8000-000000000010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>hero-banner</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>{"variant":"warm-object-study","title":"Objects In Focus","subtitle":"Twelve accessories products seeded for local editorial demos."}</t>
+        </is>
+      </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>30000000-0000-4000-8000-000000000011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>product-grid</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>{"columns":4,"productIds":["AC-001","AC-002","AC-003","AC-004","AC-005","AC-006"]}</t>
+        </is>
+      </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>30000000-0000-4000-8000-000000000012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>story-block</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>{"heading":"Finishing Pieces","body":"Bags, jewelry, belts, and softer fabric accents keep the accessories sample set balanced."}</t>
+        </is>
+      </c>
+      <c r="F13" t="b">
         <v>1</v>
       </c>
     </row>
@@ -775,7 +6539,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,7 +6567,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>880e8400-e29b-41d4-a716-446655440000</t>
+          <t>40000000-0000-4000-8000-000000000001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -823,21 +6587,941 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>880e8400-e29b-41d4-a716-446655440001</t>
+          <t>40000000-0000-4000-8000-000000000002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>SM-002</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>shop-men</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SM-003</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>shop-men</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SM-004</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>shop-men</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SM-005</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>shop-men</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SM-006</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>shop-men</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SM-007</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>shop-men</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SM-008</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>shop-men</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SM-009</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>shop-men</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SM-010</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>shop-men</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SM-011</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>shop-men</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SM-012</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>shop-men</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>AW-001</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>atelier-women</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D14">
         <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AW-002</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>atelier-women</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>AW-003</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>atelier-women</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>AW-004</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>atelier-women</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>AW-005</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>atelier-women</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>AW-006</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>atelier-women</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>AW-007</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>atelier-women</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>AW-008</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>atelier-women</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>AW-009</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>atelier-women</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>AW-010</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>atelier-women</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>AW-011</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>atelier-women</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>AW-012</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>atelier-women</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FW-001</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FW-002</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FW-003</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FW-004</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FW-005</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="D30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>FW-006</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="D31">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>FW-007</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="D32">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>FW-008</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="D33">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>FW-009</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="D34">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>FW-010</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="D35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>FW-011</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="D36">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>FW-012</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>footwear</t>
+        </is>
+      </c>
+      <c r="D37">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>AC-001</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>AC-002</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="D39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>AC-003</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="D40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>AC-004</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="D41">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>AC-005</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="D42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>AC-006</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="D43">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>AC-007</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="D44">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>AC-008</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="D45">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>AC-009</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="D46">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>AC-010</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="D47">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>AC-011</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="D48">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>40000000-0000-4000-8000-000000000048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>AC-012</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="D49">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/artifacts/import-templates/catalog-import-sample-workbook.xlsx
+++ b/artifacts/import-templates/catalog-import-sample-workbook.xlsx
@@ -299,7 +299,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -358,7 +358,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>men</t>
+          <t>mens</t>
         </is>
       </c>
     </row>
@@ -370,19 +370,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mens</t>
+          <t>nam</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>shop-men</t>
+          <t>atelier-women</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nam</t>
+          <t>Shop Women</t>
         </is>
       </c>
     </row>
@@ -394,7 +394,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Shop Women</t>
+          <t>shop-women</t>
         </is>
       </c>
     </row>
@@ -406,7 +406,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>shop-women</t>
+          <t>Women</t>
         </is>
       </c>
     </row>
@@ -418,7 +418,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>nu</t>
         </is>
       </c>
     </row>
@@ -430,31 +430,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>atelier-women</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>atelier-women</t>
+          <t>footwear</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nu</t>
+          <t>Footwear</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>atelier-women</t>
+          <t>footwear</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>atelier-women</t>
+          <t>shoes</t>
         </is>
       </c>
     </row>
@@ -466,7 +466,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Footwear</t>
+          <t>giay</t>
         </is>
       </c>
     </row>
@@ -478,43 +478,43 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>footwear</t>
+          <t>footwear-atelier</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>footwear</t>
+          <t>accessories</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>shoes</t>
+          <t>Accessories</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>footwear</t>
+          <t>accessories</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>giay</t>
+          <t>accessory</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>footwear</t>
+          <t>accessories</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>footwear-atelier</t>
+          <t>phu kien</t>
         </is>
       </c>
     </row>
@@ -525,54 +525,6 @@
         </is>
       </c>
       <c r="B19" t="inlineStr">
-        <is>
-          <t>Accessories</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>accessories</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>accessories</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>accessories</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>accessory</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>accessories</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>phu kien</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>accessories</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
         <is>
           <t>accessories-atelier</t>
         </is>
